--- a/content/script.xlsx
+++ b/content/script.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A267DA5-E099-4DBA-A16A-C301BEED3363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SceneTable" sheetId="1" r:id="rId1"/>
@@ -996,6 +996,24 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <strike val="0"/>
@@ -1059,24 +1077,6 @@
         <charset val="129"/>
       </font>
     </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1091,7 +1091,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SceneTable" displayName="SceneTable" ref="A1:G21" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SceneTable" displayName="SceneTable" ref="A1:G21" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:G21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SceneID"/>
@@ -1107,7 +1107,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DialogTable" displayName="DialogTable" ref="A1:F114" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DialogTable" displayName="DialogTable" ref="A1:F114" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:F114" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="SceneID"/>
@@ -1122,7 +1122,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ChoiceTable" displayName="ChoiceTable" ref="A1:F14" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ChoiceTable" displayName="ChoiceTable" ref="A1:F14" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:F14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="SceneID"/>
@@ -1137,7 +1137,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EvidenceTable" displayName="EvidenceTable" ref="A1:F8" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EvidenceTable" displayName="EvidenceTable" ref="A1:F8" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:F8" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="EvidenceID"/>
@@ -1152,13 +1152,13 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="enum_raw" displayName="enum_raw" ref="A1:D15" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="enum_raw" displayName="enum_raw" ref="A1:D15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A1:D15" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="EnumName" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Key" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Value" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Desc" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="EnumName" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Key" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Desc" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/content/script.xlsx
+++ b/content/script.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GSD\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A267DA5-E099-4DBA-A16A-C301BEED3363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6587030-9320-4C8F-93F6-7DD7A6C0A461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SceneTable" sheetId="1" r:id="rId1"/>
     <sheet name="DialogTable" sheetId="2" r:id="rId2"/>
-    <sheet name="ChoiceTable" sheetId="3" r:id="rId3"/>
-    <sheet name="EvidenceTable" sheetId="4" r:id="rId4"/>
-    <sheet name="$EnumView" sheetId="5" r:id="rId5"/>
-    <sheet name="$Enum" sheetId="6" r:id="rId6"/>
+    <sheet name="BranchTable" sheetId="7" r:id="rId3"/>
+    <sheet name="ChoiceTable" sheetId="3" r:id="rId4"/>
+    <sheet name="EvidenceTable" sheetId="4" r:id="rId5"/>
+    <sheet name="$EnumView" sheetId="5" r:id="rId6"/>
+    <sheet name="$Enum" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'$EnumView'!$A$1:$G$7</definedName>
+    <definedName name="ExternalData_1" localSheetId="5" hidden="1">'$EnumView'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="302">
   <si>
     <t>Key</t>
   </si>
@@ -928,13 +929,21 @@
   </si>
   <si>
     <t>'그릇은 셋. 둘은 쓰였고 하나가 남았다.' 마지막 무녀가 아직 남아 있다는 증거.</t>
+  </si>
+  <si>
+    <t>CoinditionKey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConditionValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -962,16 +971,28 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3D3D3A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -979,22 +1000,145 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -1091,7 +1235,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SceneTable" displayName="SceneTable" ref="A1:G21" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SceneTable" displayName="SceneTable" ref="A1:G21" totalsRowShown="0" headerRowDxfId="15">
   <autoFilter ref="A1:G21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SceneID"/>
@@ -1107,22 +1251,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DialogTable" displayName="DialogTable" ref="A1:F114" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:F114" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DialogTable" displayName="DialogTable" ref="A1:H114" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:H114" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="SceneID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Order"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Speaker"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Text"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Style"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Portrait"/>
+    <tableColumn id="9" xr3:uid="{6B81AF1B-8C2E-43AC-BAE8-225EB98FF06E}" name="CoinditionKey"/>
+    <tableColumn id="10" xr3:uid="{864A5DE1-6EB3-4AB5-8D26-DCD16392EAD6}" name="ConditionValue"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ChoiceTable" displayName="ChoiceTable" ref="A1:F14" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{95AFC612-B0E5-427E-A5D1-F3847BA4DB56}" name="표5" displayName="표5" ref="A1:D2" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:D2" xr:uid="{95AFC612-B0E5-427E-A5D1-F3847BA4DB56}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D554955B-A93F-48FA-9CC4-DED9D882F748}" name="SceneID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E47FE0BF-4337-4C7D-B998-7C6B744FA89B}" name="FlagKey" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{2067D4F3-D9A1-4258-80CB-24D6B366AFF2}" name="FlagValue" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{16B072EB-F967-4EC3-B923-921D66A5362A}" name="NextScene" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ChoiceTable" displayName="ChoiceTable" ref="A1:F14" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:F14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="SceneID"/>
@@ -1136,8 +1295,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EvidenceTable" displayName="EvidenceTable" ref="A1:F8" totalsRowShown="0" headerRowDxfId="6">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EvidenceTable" displayName="EvidenceTable" ref="A1:F8" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A1:F8" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="EvidenceID"/>
@@ -1151,14 +1310,14 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="enum_raw" displayName="enum_raw" ref="A1:D15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="enum_raw" displayName="enum_raw" ref="A1:D15" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:D15" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="EnumName" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Key" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Desc" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="EnumName" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Key" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Value" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Desc" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1892,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
@@ -1901,9 +2060,11 @@
     <col min="4" max="4" width="94.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8" ht="17.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1922,8 +2083,14 @@
       <c r="F1" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17.25" thickTop="1">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1937,7 +2104,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1954,7 +2121,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1971,7 +2138,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1988,7 +2155,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2005,7 +2172,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -2022,7 +2189,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2039,7 +2206,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -2056,7 +2223,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2076,7 +2243,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2096,7 +2263,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -2116,7 +2283,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2136,7 +2303,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2156,7 +2323,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2176,7 +2343,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -3974,6 +4141,46 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1CF4E4-ECEC-4EB7-B6E7-D0C53646B0EC}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -4275,7 +4482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -4454,7 +4661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -4614,7 +4821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.5"/>

--- a/content/script.xlsx
+++ b/content/script.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GSD\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6587030-9320-4C8F-93F6-7DD7A6C0A461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DA8E88-7C2E-4C7D-9AAE-D8072B31E635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="305">
   <si>
     <t>Key</t>
   </si>
@@ -931,11 +931,22 @@
     <t>'그릇은 셋. 둘은 쓰였고 하나가 남았다.' 마지막 무녀가 아직 남아 있다는 증거.</t>
   </si>
   <si>
-    <t>CoinditionKey</t>
+    <t>ConditionValue</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ConditionValue</t>
+    <t>ConditionKey</t>
+  </si>
+  <si>
+    <t>Label</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextDialogue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Order</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -943,7 +954,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -976,6 +987,14 @@
       <color rgb="FF3D3D3A"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1017,7 +1036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -1026,11 +1045,112 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF3D3D3A"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1139,88 +1259,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1235,7 +1273,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SceneTable" displayName="SceneTable" ref="A1:G21" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SceneTable" displayName="SceneTable" ref="A1:G21" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="A1:G21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SceneID"/>
@@ -1251,52 +1289,55 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DialogTable" displayName="DialogTable" ref="A1:H114" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:H114" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DialogTable" displayName="DialogTable" ref="A1:I114" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:I114" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="SceneID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Order"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Speaker"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Text"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Style"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Portrait"/>
-    <tableColumn id="9" xr3:uid="{6B81AF1B-8C2E-43AC-BAE8-225EB98FF06E}" name="CoinditionKey"/>
+    <tableColumn id="9" xr3:uid="{6B81AF1B-8C2E-43AC-BAE8-225EB98FF06E}" name="ConditionKey"/>
     <tableColumn id="10" xr3:uid="{864A5DE1-6EB3-4AB5-8D26-DCD16392EAD6}" name="ConditionValue"/>
+    <tableColumn id="7" xr3:uid="{1E0FF57E-696E-43E8-A80C-8F27FFC04612}" name="Label"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{95AFC612-B0E5-427E-A5D1-F3847BA4DB56}" name="표5" displayName="표5" ref="A1:D2" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:D2" xr:uid="{95AFC612-B0E5-427E-A5D1-F3847BA4DB56}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D554955B-A93F-48FA-9CC4-DED9D882F748}" name="SceneID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{E47FE0BF-4337-4C7D-B998-7C6B744FA89B}" name="FlagKey" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{2067D4F3-D9A1-4258-80CB-24D6B366AFF2}" name="FlagValue" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{16B072EB-F967-4EC3-B923-921D66A5362A}" name="NextScene" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{95AFC612-B0E5-427E-A5D1-F3847BA4DB56}" name="표5" displayName="표5" ref="A1:E2" insertRow="1" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:E2" xr:uid="{95AFC612-B0E5-427E-A5D1-F3847BA4DB56}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D554955B-A93F-48FA-9CC4-DED9D882F748}" name="SceneID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{E47FE0BF-4337-4C7D-B998-7C6B744FA89B}" name="FlagKey" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{2067D4F3-D9A1-4258-80CB-24D6B366AFF2}" name="FlagValue" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{16B072EB-F967-4EC3-B923-921D66A5362A}" name="NextScene" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E8EF499F-3C23-4C62-B7CE-A92B48F7309C}" name="Order" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ChoiceTable" displayName="ChoiceTable" ref="A1:F14" totalsRowShown="0" headerRowDxfId="13">
-  <autoFilter ref="A1:F14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ChoiceTable" displayName="ChoiceTable" ref="A1:G14" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A1:G14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="SceneID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Order"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Text"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="FlagKey"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="FlagValue"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="NextScene"/>
+    <tableColumn id="7" xr3:uid="{B9E0727F-80A1-4E1A-A9E0-0F3EDB6F2215}" name="NextDialogue"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EvidenceTable" displayName="EvidenceTable" ref="A1:F8" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EvidenceTable" displayName="EvidenceTable" ref="A1:F8" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:F8" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="EvidenceID"/>
@@ -1311,13 +1352,13 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="enum_raw" displayName="enum_raw" ref="A1:D15" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="enum_raw" displayName="enum_raw" ref="A1:D15" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:D15" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="EnumName" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Key" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Value" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Desc" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="EnumName" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Key" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Value" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Desc" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2051,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
@@ -2064,7 +2105,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" thickBot="1">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -2084,13 +2125,16 @@
         <v>90</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="17.25" thickTop="1">
+      <c r="I1" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" thickTop="1">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -2104,7 +2148,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -2121,7 +2165,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -2138,7 +2182,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -2155,7 +2199,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2172,7 +2216,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -2189,7 +2233,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2206,7 +2250,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -2223,7 +2267,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2243,7 +2287,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2263,7 +2307,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -2283,7 +2327,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2303,7 +2347,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2323,7 +2367,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2343,7 +2387,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -4142,7 +4186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1CF4E4-ECEC-4EB7-B6E7-D0C53646B0EC}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -4151,7 +4195,7 @@
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
         <v>32</v>
       </c>
@@ -4164,12 +4208,16 @@
       <c r="D1" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4182,7 +4230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
@@ -4191,9 +4239,10 @@
     <col min="4" max="4" width="14.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -4212,8 +4261,11 @@
       <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -4233,7 +4285,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -4253,7 +4305,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -4273,7 +4325,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -4293,7 +4345,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -4313,7 +4365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -4333,7 +4385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -4353,7 +4405,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -4373,7 +4425,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -4393,7 +4445,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>73</v>
       </c>
@@ -4413,7 +4465,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -4433,7 +4485,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -4453,7 +4505,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>80</v>
       </c>
